--- a/xls/square_16_tri3_13.xlsx
+++ b/xls/square_16_tri3_13.xlsx
@@ -482,13 +482,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>0.8190598371059914</v>
+        <v>0.8190597764078251</v>
       </c>
       <c r="J13">
-        <v>-1.8990598267233285</v>
+        <v>-1.8990598539944334</v>
       </c>
       <c r="K13">
-        <v>-0.8101965261118053</v>
+        <v>-0.8101966180132888</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-2.2753026108159853</v>
+        <v>-2.2753021256113644</v>
       </c>
       <c r="J14">
-        <v>-2.0929369962057636</v>
+        <v>-2.092936972043212</v>
       </c>
       <c r="K14">
-        <v>-1.47621465975521</v>
+        <v>-1.4762147488710085</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.261587470784869</v>
+        <v>-2.261587590730082</v>
       </c>
       <c r="J15">
-        <v>-2.0964416040136307</v>
+        <v>-2.096441617725268</v>
       </c>
       <c r="K15">
-        <v>-1.4896476893279713</v>
+        <v>-1.4896478494512093</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.255273244033629</v>
+        <v>-2.2552732366640544</v>
       </c>
       <c r="J16">
-        <v>-2.0778231823991296</v>
+        <v>-2.077823173518579</v>
       </c>
       <c r="K16">
-        <v>-1.3236399896490527</v>
+        <v>-1.323639860693957</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-2.232566554369754</v>
+        <v>-2.2325663705089416</v>
       </c>
       <c r="J17">
-        <v>-1.8303309746583505</v>
+        <v>-1.8303309011408582</v>
       </c>
       <c r="K17">
-        <v>1.10700812302567</v>
+        <v>1.107005443724964</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-2.0635797135335903</v>
+        <v>-2.0635792070953776</v>
       </c>
       <c r="J18">
-        <v>-1.6147664256074996</v>
+        <v>-1.6147662915211556</v>
       </c>
       <c r="K18">
-        <v>1.4483335699463786</v>
+        <v>1.4483338646473773</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.7826882217153063</v>
+        <v>-0.7826881028320517</v>
       </c>
       <c r="J19">
-        <v>-0.7205238769819486</v>
+        <v>-0.7205237900464688</v>
       </c>
       <c r="K19">
-        <v>3.7149939467400848</v>
+        <v>3.714993925284224</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.04730807559454751</v>
+        <v>-0.04730807450038067</v>
       </c>
       <c r="J20">
-        <v>-0.04545214351650359</v>
+        <v>-0.04545214249351952</v>
       </c>
       <c r="K20">
-        <v>3.7229698009357888</v>
+        <v>3.7229697915885764</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.010030736595496192</v>
+        <v>-0.010030736636883595</v>
       </c>
       <c r="J21">
-        <v>-0.009055688158614145</v>
+        <v>-0.00905568818470023</v>
       </c>
       <c r="K21">
-        <v>3.4013899931504405</v>
+        <v>3.4013899938128285</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>0.00014439769716340946</v>
+        <v>0.00014439769811112465</v>
       </c>
       <c r="J22">
-        <v>2.2328840334835602e-5</v>
+        <v>2.2328840783224822e-5</v>
       </c>
       <c r="K22">
-        <v>2.4812092902302756</v>
+        <v>2.4812092909419015</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -832,13 +832,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.00013556733372639722</v>
+        <v>-0.00013556733375490198</v>
       </c>
       <c r="J23">
-        <v>-9.283613088499053e-5</v>
+        <v>-9.283613090331666e-5</v>
       </c>
       <c r="K23">
-        <v>2.289805890734842</v>
+        <v>2.28980589104103</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-9.989377694484234e-5</v>
+        <v>-9.989377694243096e-5</v>
       </c>
       <c r="J24">
-        <v>-8.202310011683446e-5</v>
+        <v>-8.202310011582172e-5</v>
       </c>
       <c r="K24">
-        <v>2.342341048125148</v>
+        <v>2.3423410479173223</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -902,13 +902,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>1.4827203064500221e-5</v>
+        <v>1.4827203063632357e-5</v>
       </c>
       <c r="J25">
         <v>3.702375504618243e-6</v>
       </c>
       <c r="K25">
-        <v>1.9403994513758616</v>
+        <v>1.9403994512616702</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -937,13 +937,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-4.975728505442049e-5</v>
+        <v>-4.975728505398649e-5</v>
       </c>
       <c r="J26">
-        <v>-3.117798639976649e-5</v>
+        <v>-3.117798639971827e-5</v>
       </c>
       <c r="K26">
-        <v>1.9452772301610588</v>
+        <v>1.945277230188398</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -972,13 +972,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>4.871876091053795e-7</v>
+        <v>4.871876092018122e-7</v>
       </c>
       <c r="J27">
-        <v>-1.4619295094318436e-7</v>
+        <v>-1.46192950894968e-7</v>
       </c>
       <c r="K27">
-        <v>1.4155607893572844</v>
+        <v>1.4155607895471847</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1010,10 +1010,10 @@
         <v>-3.4599044469860806e-7</v>
       </c>
       <c r="J28">
-        <v>-4.952994441011306e-7</v>
+        <v>-4.952994440046978e-7</v>
       </c>
       <c r="K28">
-        <v>1.3564218874689085</v>
+        <v>1.3564218875186145</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-5.56034373716066e-7</v>
+        <v>-5.560343738124988e-7</v>
       </c>
       <c r="J29">
-        <v>-4.999326633755996e-7</v>
+        <v>-4.999326630863011e-7</v>
       </c>
       <c r="K29">
-        <v>1.2736727940894428</v>
+        <v>1.273672794129053</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-4.419179037577103e-7</v>
+        <v>-4.4191790346841175e-7</v>
       </c>
       <c r="J30">
-        <v>-3.722531782400825e-7</v>
+        <v>-3.722531781436497e-7</v>
       </c>
       <c r="K30">
-        <v>1.187768768240043</v>
+        <v>1.187768768308857</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-2.607019691184518e-7</v>
+        <v>-2.6070196921488463e-7</v>
       </c>
       <c r="J31">
-        <v>-2.613381864755451e-7</v>
+        <v>-2.613381867166271e-7</v>
       </c>
       <c r="K31">
-        <v>1.1634212425372634</v>
+        <v>1.1634212426927732</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-8.828531988545344e-8</v>
+        <v>-8.828531983723706e-8</v>
       </c>
       <c r="J32">
-        <v>-2.3923830355752805e-7</v>
+        <v>-2.392383037503937e-7</v>
       </c>
       <c r="K32">
-        <v>1.2585027489348828</v>
+        <v>1.258502748726304</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_13.xlsx
+++ b/xls/square_16_tri3_13.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>196</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>289</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>726</v>
+      </c>
+      <c r="I11">
+        <v>5.219700844655665</v>
+      </c>
+      <c r="J11">
+        <v>1.2372874201045485</v>
+      </c>
+      <c r="K11">
+        <v>1.9058080117240033</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>196</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>289</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>864</v>
+      </c>
+      <c r="I12">
+        <v>3.806054913844804</v>
+      </c>
+      <c r="J12">
+        <v>0.2644137147298111</v>
+      </c>
+      <c r="K12">
+        <v>1.1759267825015607</v>
+      </c>
+    </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
